--- a/output/pdf_financials_xlsx/NURL.xlsx
+++ b/output/pdf_financials_xlsx/NURL.xlsx
@@ -1649,10 +1649,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.437706</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0.096498</v>
+        <v>0.8877660000000001</v>
       </c>
     </row>
     <row r="93">
@@ -2708,7 +2708,11 @@
           <t>Reserve for warrants 7</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" s="5" t="n">
         <v>0.437706</v>
       </c>

--- a/output/pdf_financials_xlsx/NURL.xlsx
+++ b/output/pdf_financials_xlsx/NURL.xlsx
@@ -879,10 +879,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.066789</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.165376</v>
       </c>
     </row>
     <row r="35">
@@ -905,10 +905,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.066789</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.165376</v>
       </c>
     </row>
     <row r="37">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
